--- a/data/DOC-20251215-WA0003..xlsx
+++ b/data/DOC-20251215-WA0003..xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Descargas\Acciona Facility Services\Aplicaciones Webs\mi-app-qr\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2ABB6D-9BDA-4434-813C-5E0371DB883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3916FA21-02BF-458B-8497-7652A856C0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="21480" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6309" uniqueCount="4387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6311" uniqueCount="4389">
   <si>
     <t>ID_ACTIVO_ARBOL</t>
   </si>
@@ -13181,6 +13181,12 @@
   </si>
   <si>
     <t>GOH</t>
+  </si>
+  <si>
+    <t>CC01_U111021</t>
+  </si>
+  <si>
+    <t>2465 MCS Steerable Wheel Divert</t>
   </si>
 </sst>
 </file>
@@ -13479,7 +13485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3154"/>
+  <dimension ref="A1:C3155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -48182,6 +48188,17 @@
         <v>4386</v>
       </c>
     </row>
+    <row r="3155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3155">
+        <v>243574</v>
+      </c>
+      <c r="B3155" t="s">
+        <v>4387</v>
+      </c>
+      <c r="C3155" t="s">
+        <v>4388</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
